--- a/tests/e2e/fixtures/tpl-real-like.xlsx
+++ b/tests/e2e/fixtures/tpl-real-like.xlsx
@@ -68,7 +68,7 @@
     <t>〒000-0000</t>
   </si>
   <si>
-    <t>○○県○○市中央7-3-40　00コーポ1号</t>
+    <t>東京都架空区見本台1-2-3　00コーポ1号</t>
   </si>
   <si>
     <t>TEL000-0000-0000</t>

--- a/tests/e2e/fixtures/tpl-real-like.xlsx
+++ b/tests/e2e/fixtures/tpl-real-like.xlsx
@@ -48,7 +48,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>エスプリ　アマン　御中</t>
+    <t>カレホン　カレホ　御中</t>
     <rPh sb="9" eb="11">
       <t>オンチュウ</t>
     </rPh>

--- a/tests/e2e/fixtures/tpl-real-like.xlsx
+++ b/tests/e2e/fixtures/tpl-real-like.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeroa\nomiya-app-test\tests\e2e\fixtures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{CC0BDFAA-2B41-4440-9AE2-5CD28C2893F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
